--- a/output/pdf_financials_xlsx/THRM.xlsx
+++ b/output/pdf_financials_xlsx/THRM.xlsx
@@ -5264,43 +5264,43 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.875458</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.907229</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.646701</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.646701</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.424226</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.229336</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>5.346669</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.363669</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>8.258839</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>13.625939</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>13.715939</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>14.014949</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>14.185889</v>
       </c>
     </row>
     <row r="93">
@@ -9214,7 +9214,11 @@
           <t>Warrants reserve (note 16)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -9298,7 +9302,11 @@
           <t>Share-based payments reserve (note 17)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -11036,7 +11044,11 @@
           <t>Warrants reserve (note 15)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -11120,7 +11132,11 @@
           <t>Share-based payments reserve (note 16)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -12550,7 +12566,11 @@
           <t>Warrants reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -12634,7 +12654,11 @@
           <t>Share based payments reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -13580,7 +13604,11 @@
           <t>Warrants reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -13664,7 +13692,11 @@
           <t>Share based payments reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -14264,7 +14296,11 @@
           <t>Warrants reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -14346,7 +14382,11 @@
           <t>Share based payments reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -15166,7 +15206,11 @@
           <t>Warrants reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -15248,7 +15292,11 @@
           <t>Share based payments reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -15502,7 +15550,11 @@
           <t>Warrants reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -15586,7 +15638,11 @@
           <t>Share based payments reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -16804,7 +16860,11 @@
           <t>Warrants reserve (Note 10) 107,778</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -16890,7 +16950,11 @@
           <t>Share based payments reserve (Note 10) 767,680</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/THRM.xlsx
+++ b/output/pdf_financials_xlsx/THRM.xlsx
@@ -998,13 +998,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.021843</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.020055</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.005041</v>
       </c>
     </row>
     <row r="13">
@@ -1873,13 +1873,13 @@
         <v>-5.881072</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.767772</v>
+        <v>-3.789615</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.451307</v>
+        <v>-2.471362</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.342907</v>
+        <v>-4.347948</v>
       </c>
     </row>
     <row r="28">
@@ -1979,13 +1979,13 @@
         <v>-5.881072</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.843152</v>
+        <v>-3.864995</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.550821</v>
+        <v>-2.570876</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.434689</v>
+        <v>-4.43973</v>
       </c>
     </row>
     <row r="30">
@@ -2034,13 +2034,13 @@
         <v>-4218.029506480094</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-186923.7354085603</v>
+        <v>-187986.1381322957</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-42407.66417290108</v>
+        <v>-42741.08063175395</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-5894.997873132344</v>
+        <v>-5901.698835539958</v>
       </c>
     </row>
     <row r="31">
@@ -2172,43 +2172,43 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.051652</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.021488</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>6.3e-05</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.000117</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.065499</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.224701</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.030397</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.061767</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.780847</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>3.081776</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.182235</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.001096</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.001467</v>
       </c>
     </row>
     <row r="35">
@@ -2274,43 +2274,43 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.051652</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.021488</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>6.3e-05</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.000117</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.065499</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.224701</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.030397</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.061767</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.780847</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>3.081776</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.182235</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.001096</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.036606</v>
+        <v>0.038073</v>
       </c>
     </row>
     <row r="37">
@@ -2886,43 +2886,43 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.668079</v>
+        <v>5.616427</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.566578</v>
+        <v>5.54509</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>6.3e-05</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.000117</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.150892</v>
+        <v>0.085393</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.291752</v>
+        <v>0.067051</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.033334</v>
+        <v>0.002937</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.084279</v>
+        <v>0.022512</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.90231</v>
+        <v>0.121463</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.296099</v>
+        <v>0.214323</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.27316</v>
+        <v>0.09092500000000001</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.219565</v>
+        <v>0.218469</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.029623</v>
+        <v>0.028156</v>
       </c>
     </row>
     <row r="49">
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0336</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0336</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.028</v>
       </c>
     </row>
     <row r="125">
@@ -6963,13 +6963,13 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0336</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0336</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.028</v>
       </c>
     </row>
     <row r="126">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -18914,7 +18914,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -26152,7 +26156,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -27096,7 +27100,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -27868,7 +27872,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -28214,7 +28218,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">

--- a/output/pdf_financials_xlsx/THRM.xlsx
+++ b/output/pdf_financials_xlsx/THRM.xlsx
@@ -556,10 +556,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0.001709</v>
@@ -607,10 +605,8 @@
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0.000439</v>
@@ -662,10 +658,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0.00127</v>
@@ -713,10 +707,8 @@
       <c r="C7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -764,10 +756,8 @@
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -815,10 +805,8 @@
       <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -866,10 +854,8 @@
       <c r="C10" s="3" t="n">
         <v>0.868757</v>
       </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.355757</v>
@@ -917,10 +903,8 @@
       <c r="C11" s="3" t="n">
         <v>-0.868757</v>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D11" s="3" t="n">
+        <v>-1.084876</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-0.354487</v>
@@ -968,10 +952,8 @@
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1019,10 +1001,8 @@
       <c r="C13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>-0</v>
@@ -1070,10 +1050,8 @@
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
@@ -1121,10 +1099,8 @@
       <c r="C15" s="3" t="n">
         <v>-0.021048</v>
       </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D15" s="3" t="n">
+        <v>0.00194</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>-0.001884</v>
@@ -1166,20 +1142,14 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.776487</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0.860044</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0.068208</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-0.356371</v>
@@ -1227,10 +1197,8 @@
       <c r="C17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1426,20 +1394,14 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.776487</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0.860044</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.068208</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.356371</v>
@@ -1487,10 +1449,8 @@
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -1538,10 +1498,8 @@
       <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
@@ -1583,20 +1541,14 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.776487</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0.860044</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.068208</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-0.356371</v>
@@ -1833,20 +1785,14 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.776487</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0.860044</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0.068208</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.356371</v>
@@ -1894,10 +1840,8 @@
       <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
@@ -1939,20 +1883,14 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.776487</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0.860044</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0.068208</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.356371</v>
@@ -2049,20 +1987,14 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -3915,16 +3847,14 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0.264872</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.492859</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.862386</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>0</v>
@@ -5591,20 +5521,14 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.776487</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>0.860044</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>0.068208</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-0.356371</v>
@@ -5652,10 +5576,8 @@
       <c r="C100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -5703,10 +5625,8 @@
       <c r="C101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>-0.000182</v>
@@ -5754,10 +5674,8 @@
       <c r="C102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E102" s="3" t="n">
         <v>0.0001</v>
@@ -5805,10 +5723,8 @@
       <c r="C103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>0.000833</v>
@@ -5856,10 +5772,8 @@
       <c r="C104" s="3" t="n">
         <v>0.234641</v>
       </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D104" s="3" t="n">
+        <v>-0.794445</v>
       </c>
       <c r="E104" s="3" t="n">
         <v>0.270862</v>
@@ -5907,10 +5821,8 @@
       <c r="C105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E105" s="3" t="n">
         <v>0</v>
@@ -5958,10 +5870,8 @@
       <c r="C106" s="3" t="n">
         <v>0.234641</v>
       </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D106" s="3" t="n">
+        <v>-0.794445</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.271613</v>
@@ -6009,10 +5919,8 @@
       <c r="C107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E107" s="3" t="n">
         <v>0</v>
@@ -6021,7 +5929,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>0.475</v>
       </c>
       <c r="H107" s="3" t="n">
         <v>0.614667</v>
@@ -6060,10 +5968,8 @@
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E108" s="3" t="n">
         <v>0</v>
@@ -6111,10 +6017,8 @@
       <c r="C109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E109" s="3" t="n">
         <v>0</v>
@@ -6162,10 +6066,8 @@
       <c r="C110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -6177,19 +6079,19 @@
         <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.008737</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.018907</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.017397</v>
       </c>
       <c r="K110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.001383</v>
       </c>
       <c r="M110" s="3" t="n">
         <v>0</v>
@@ -6213,10 +6115,8 @@
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -6237,7 +6137,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -6264,10 +6164,8 @@
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -6315,10 +6213,8 @@
       <c r="C113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E113" s="3" t="n">
         <v>0</v>
@@ -6366,10 +6262,8 @@
       <c r="C114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E114" s="3" t="n">
         <v>0</v>
@@ -6417,10 +6311,8 @@
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -6468,10 +6360,8 @@
       <c r="C116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
@@ -6483,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.04949</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>0</v>
@@ -6492,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="L116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.26756</v>
       </c>
       <c r="N116" s="3" t="n">
         <v>0</v>
@@ -6519,10 +6409,8 @@
       <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E117" s="3" t="n">
         <v>0</v>
@@ -6570,10 +6458,8 @@
       <c r="C118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
@@ -6620,10 +6506,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
@@ -6678,10 +6562,8 @@
       <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
         <v>0</v>
@@ -6729,10 +6611,8 @@
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
@@ -6780,10 +6660,8 @@
       <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E122" s="3" t="n">
         <v>0</v>
@@ -6831,10 +6709,8 @@
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E123" s="3" t="n">
         <v>0</v>
@@ -6882,10 +6758,8 @@
       <c r="C124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -6933,10 +6807,8 @@
       <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -6984,10 +6856,8 @@
       <c r="C126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E126" s="3" t="n">
         <v>0</v>
@@ -7112,10 +6982,8 @@
       <c r="C128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E128" s="3" t="n">
         <v>0</v>
@@ -7162,15 +7030,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C129" s="3" t="n">
+        <v>0.135005</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>0.025</v>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
@@ -7220,10 +7084,8 @@
       <c r="C130" s="3" t="n">
         <v>0.000748</v>
       </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D130" s="3" t="n">
+        <v>0.051652</v>
       </c>
       <c r="E130" s="3" t="n">
         <v>0.021488</v>
@@ -7271,10 +7133,8 @@
       <c r="C131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E131" s="3" t="n">
         <v>0</v>
@@ -7322,10 +7182,8 @@
       <c r="C132" s="3" t="n">
         <v>0.050904</v>
       </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D132" s="3" t="n">
+        <v>-0.030164</v>
       </c>
       <c r="E132" s="3" t="n">
         <v>-0.021425</v>
@@ -7373,10 +7231,8 @@
       <c r="C133" s="3" t="n">
         <v>0.051652</v>
       </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D133" s="3" t="n">
+        <v>0.021488</v>
       </c>
       <c r="E133" s="3" t="n">
         <v>6.3e-05</v>
@@ -7424,10 +7280,8 @@
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -7448,7 +7302,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -7501,7 +7355,7 @@
         <v>-0.104944</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-2.855507</v>
+        <v>-2.955507</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-3.800002</v>
@@ -7527,7 +7381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R298"/>
+  <dimension ref="A1:R313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19946,7 +19800,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>PurchaseOfIntangibles</t>
+          <t>NetIntangiblesPurchaseAndSale</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -20548,7 +20402,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -21382,7 +21240,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -21468,7 +21330,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -21800,7 +21666,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -22368,7 +22238,11 @@
           <t>Debenture accretion expense</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -22958,7 +22832,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>PurchaseOfIntangibles</t>
+          <t>NetIntangiblesPurchaseAndSale</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -23990,7 +23864,11 @@
           <t>Stock options expense</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -24162,7 +24040,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>PurchaseOfIntangibles</t>
+          <t>NetIntangiblesPurchaseAndSale</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -25368,25 +25246,29 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>OPERA TING ACTIVITIES</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Net income (loss) $</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" s="5" t="n">
-        <v>-0.776487</v>
+          <t>NET INCOME $</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F209" s="5" t="n">
         <v>0.860044</v>
       </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G209" s="5" t="n">
+        <v>0.068208</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -25452,25 +25334,29 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>Sales taxes recoverable                                                 (28,331)</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Management and performance fees payable</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" s="5" t="n">
-        <v>0.028077</v>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F210" s="5" t="n">
-        <v>-1.735455</v>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.234641</v>
+      </c>
+      <c r="G210" s="5" t="n">
+        <v>-0.794445</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -25536,25 +25422,25 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>Management and performance fees payable                                         (1,735,455)</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Unpaid interest capitalized</t>
+          <t>Loans from directors</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
-      <c r="E211" s="5" t="n">
-        <v>0.473022</v>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F211" s="5" t="n">
-        <v>0.550989</v>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00568</v>
+      </c>
+      <c r="G211" s="5" t="n">
+        <v>0.024496</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -25620,29 +25506,25 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>Management and performance fees payable                                         (1,735,455)</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Cash flow used by operating activities</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E212" s="5" t="n">
-        <v>-0.000435</v>
+          <t>Unpaid interest capitalized</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F212" s="5" t="n">
-        <v>-0.084101</v>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.550989</v>
+      </c>
+      <c r="G212" s="5" t="n">
+        <v>0.64397</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -25708,15 +25590,19 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITY</t>
+          <t>Convertible debentures issued - net                                      25,000</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Issuance of share capital</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
+          <t>Cash flow from financing activities</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -25725,10 +25611,8 @@
       <c r="F213" s="5" t="n">
         <v>0.135005</v>
       </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G213" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -25794,12 +25678,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITY</t>
+          <t>Convertible debentures issued - net                                      25,000</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>INCREASE (DECREASE) IN CASH</t>
+          <t>(DECREASE) INCREASE IN CASH</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25807,16 +25691,16 @@
           <t>ChangesInCash</t>
         </is>
       </c>
-      <c r="E214" s="5" t="n">
-        <v>-0.000435</v>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F214" s="5" t="n">
         <v>0.050904</v>
       </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G214" s="5" t="n">
+        <v>-0.030164</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -25882,7 +25766,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITY</t>
+          <t>Convertible debentures issued - net                                      25,000</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -25895,16 +25779,16 @@
           <t>BeginningCashPosition</t>
         </is>
       </c>
-      <c r="E215" s="5" t="n">
-        <v>0.001183</v>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F215" s="5" t="n">
         <v>0.000748</v>
       </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G215" s="5" t="n">
+        <v>0.051652</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -25970,7 +25854,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITY</t>
+          <t>Convertible debentures issued - net                                      25,000</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -25983,16 +25867,16 @@
           <t>EndCashPosition</t>
         </is>
       </c>
-      <c r="E216" s="5" t="n">
-        <v>0.000748</v>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F216" s="5" t="n">
         <v>0.051652</v>
       </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G216" s="5" t="n">
+        <v>0.021488</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -26053,33 +25937,29 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Sales $</t>
+          <t>Net income (loss) $</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="n">
+        <v>-0.776487</v>
+      </c>
+      <c r="F217" s="5" t="n">
+        <v>0.860044</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -26131,43 +26011,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q217" s="5" t="n">
-        <v>0.006015</v>
-      </c>
-      <c r="R217" s="5" t="n">
-        <v>0.075228</v>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Management and performance fees payable</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" s="5" t="n">
+        <v>0.028077</v>
+      </c>
+      <c r="F218" s="5" t="n">
+        <v>-1.735455</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -26219,43 +26095,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q218" s="5" t="n">
-        <v>0.020055</v>
-      </c>
-      <c r="R218" s="5" t="n">
-        <v>0.005041</v>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Total revenue</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Unpaid interest capitalized</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" s="5" t="n">
+        <v>0.473022</v>
+      </c>
+      <c r="F219" s="5" t="n">
+        <v>0.550989</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -26302,46 +26174,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P219" s="5" t="n">
-        <v>0.023899</v>
-      </c>
-      <c r="Q219" s="5" t="n">
-        <v>0.02607</v>
-      </c>
-      <c r="R219" s="5" t="n">
-        <v>0.08026899999999999</v>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Cash flow used by operating activities</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="n">
+        <v>-0.000435</v>
+      </c>
+      <c r="F220" s="5" t="n">
+        <v>-0.084101</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -26393,43 +26267,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q220" s="5" t="n">
-        <v>0.000614</v>
-      </c>
-      <c r="R220" s="5" t="n">
-        <v>0.025418</v>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>FINANCING ACTIVITY</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
+          <t>Issuance of share capital</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F221" s="5" t="n">
+        <v>0.135005</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -26476,46 +26348,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P221" s="5" t="n">
-        <v>0.023899</v>
-      </c>
-      <c r="Q221" s="5" t="n">
-        <v>0.025456</v>
-      </c>
-      <c r="R221" s="5" t="n">
-        <v>0.054851</v>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>FINANCING ACTIVITY</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>INCREASE (DECREASE) IN CASH</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="n">
+        <v>-0.000435</v>
+      </c>
+      <c r="F222" s="5" t="n">
+        <v>0.050904</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -26562,46 +26436,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P222" s="5" t="n">
-        <v>3.180457</v>
-      </c>
-      <c r="Q222" s="5" t="n">
-        <v>0.852114</v>
-      </c>
-      <c r="R222" s="5" t="n">
-        <v>1.560116</v>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>FINANCING ACTIVITY</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Research and development</t>
+          <t>CASH - BEGINNING OF YEAR</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>ResearchAndDevelopment</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="n">
+        <v>0.001183</v>
+      </c>
+      <c r="F223" s="5" t="n">
+        <v>0.000748</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -26648,11 +26524,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P223" s="5" t="n">
-        <v>0.446577</v>
-      </c>
-      <c r="Q223" s="5" t="n">
-        <v>0.009690000000000001</v>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R223" t="inlineStr">
         <is>
@@ -26663,29 +26543,29 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>FINANCING ACTIVITY</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 17)</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CASH - END OF YEAR $</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="n">
+        <v>0.000748</v>
+      </c>
+      <c r="F224" s="5" t="n">
+        <v>0.051652</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -26737,11 +26617,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q224" s="5" t="n">
-        <v>0.29901</v>
-      </c>
-      <c r="R224" s="5" t="n">
-        <v>0.17094</v>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="225">
@@ -26752,17 +26636,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Total operating expenses</t>
+          <t>Sales $</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -26820,14 +26704,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P225" s="5" t="n">
-        <v>3.627034</v>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q225" s="5" t="n">
-        <v>1.160814</v>
+        <v>0.006015</v>
       </c>
       <c r="R225" s="5" t="n">
-        <v>1.731056</v>
+        <v>0.075228</v>
       </c>
     </row>
     <row r="226">
@@ -26838,17 +26724,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Loss from operations</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -26906,14 +26792,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P226" s="5" t="n">
-        <v>-3.603135</v>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q226" s="5" t="n">
-        <v>-1.135358</v>
+        <v>0.020055</v>
       </c>
       <c r="R226" s="5" t="n">
-        <v>-1.676205</v>
+        <v>0.005041</v>
       </c>
     </row>
     <row r="227">
@@ -26924,15 +26812,19 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Loss on settlement (note 15)</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>Total revenue</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -26988,16 +26880,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P227" s="5" t="n">
+        <v>0.023899</v>
       </c>
       <c r="Q227" s="5" t="n">
-        <v>-0.1925</v>
+        <v>0.02607</v>
       </c>
       <c r="R227" s="5" t="n">
-        <v>-0.000549</v>
+        <v>0.08026899999999999</v>
       </c>
     </row>
     <row r="228">
@@ -27008,15 +26898,19 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Loss on foreign currency translation</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -27072,14 +26966,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P228" s="5" t="n">
-        <v>-0.016835</v>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q228" s="5" t="n">
-        <v>-0.005924</v>
+        <v>0.000614</v>
       </c>
       <c r="R228" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.025418</v>
       </c>
     </row>
     <row r="229">
@@ -27090,17 +26986,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Interest expense (note 14)</t>
+          <t>Gross profit</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>GrossProfit</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -27158,16 +27054,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P229" s="5" t="n">
+        <v>0.023899</v>
       </c>
       <c r="Q229" s="5" t="n">
-        <v>-0.008604000000000001</v>
+        <v>0.025456</v>
       </c>
       <c r="R229" s="5" t="n">
-        <v>-0.002608</v>
+        <v>0.054851</v>
       </c>
     </row>
     <row r="230">
@@ -27178,15 +27072,19 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Unrealized loss on marketable securities (note 5)</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -27242,18 +27140,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P230" s="5" t="n">
+        <v>3.180457</v>
+      </c>
+      <c r="Q230" s="5" t="n">
+        <v>0.852114</v>
       </c>
       <c r="R230" s="5" t="n">
-        <v>-0.029951</v>
+        <v>1.560116</v>
       </c>
     </row>
     <row r="231">
@@ -27264,17 +27158,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Depreciation and amortization (notes 9, 10 and 11)</t>
+          <t>Research and development</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>ResearchAndDevelopment</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -27332,16 +27226,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P231" s="5" t="n">
+        <v>0.446577</v>
       </c>
       <c r="Q231" s="5" t="n">
-        <v>-0.09951400000000001</v>
-      </c>
-      <c r="R231" s="5" t="n">
-        <v>-0.091782</v>
+        <v>0.009690000000000001</v>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="232">
@@ -27352,12 +27246,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Change in fair value of investments (note 8)</t>
+          <t>Stock-based compensation (note 17)</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -27422,10 +27316,10 @@
         </is>
       </c>
       <c r="Q232" s="5" t="n">
-        <v>0.178198</v>
+        <v>0.29901</v>
       </c>
       <c r="R232" s="5" t="n">
-        <v>-2.118992</v>
+        <v>0.17094</v>
       </c>
     </row>
     <row r="233">
@@ -27436,15 +27330,19 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Impairment of promissory note receivable (note 7)</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -27500,18 +27398,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P233" s="5" t="n">
+        <v>3.627034</v>
       </c>
       <c r="Q233" s="5" t="n">
-        <v>-0.12993</v>
-      </c>
-      <c r="R233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.160814</v>
+      </c>
+      <c r="R233" s="5" t="n">
+        <v>1.731056</v>
       </c>
     </row>
     <row r="234">
@@ -27522,15 +27416,19 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Impairment of intangible assets (note 10)</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>Loss from operations</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -27586,16 +27484,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P234" s="5" t="n">
+        <v>-3.603135</v>
       </c>
       <c r="Q234" s="5" t="n">
-        <v>-1.057675</v>
+        <v>-1.135358</v>
       </c>
       <c r="R234" s="5" t="n">
-        <v>-0.42162</v>
+        <v>-1.676205</v>
       </c>
     </row>
     <row r="235">
@@ -27611,14 +27507,10 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss on settlement (note 15)</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -27674,14 +27566,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P235" s="5" t="n">
-        <v>-3.767772</v>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q235" s="5" t="n">
-        <v>-2.451307</v>
+        <v>-0.1925</v>
       </c>
       <c r="R235" s="5" t="n">
-        <v>-4.342907</v>
+        <v>-0.000549</v>
       </c>
     </row>
     <row r="236">
@@ -27697,7 +27591,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per share (note 19) $</t>
+          <t>Loss on foreign currency translation</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -27756,16 +27650,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P236" s="5" t="n">
+        <v>-0.016835</v>
       </c>
       <c r="Q236" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>-0.005924</v>
       </c>
       <c r="R236" s="5" t="n">
-        <v>-8e-08</v>
+        <v>-0.0012</v>
       </c>
     </row>
     <row r="237">
@@ -27776,17 +27668,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Interest expense (note 14)</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -27844,14 +27736,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P237" s="5" t="n">
-        <v>240.269604</v>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q237" s="5" t="n">
-        <v>39.780238</v>
+        <v>-0.008604000000000001</v>
       </c>
       <c r="R237" s="5" t="n">
-        <v>56.100295</v>
+        <v>-0.002608</v>
       </c>
     </row>
     <row r="238">
@@ -27862,19 +27756,15 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Interest income $</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Unrealized loss on marketable securities (note 5)</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -27930,16 +27820,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P238" s="5" t="n">
-        <v>0.021843</v>
-      </c>
-      <c r="Q238" s="5" t="n">
-        <v>0.020055</v>
-      </c>
-      <c r="R238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R238" s="5" t="n">
+        <v>-0.029951</v>
       </c>
     </row>
     <row r="239">
@@ -27950,17 +27842,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Depreciation and amortization (notes 9, 10 and 11)</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -28018,16 +27910,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P239" s="5" t="n">
-        <v>0.002056</v>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q239" s="5" t="n">
-        <v>0.006015</v>
-      </c>
-      <c r="R239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.09951400000000001</v>
+      </c>
+      <c r="R239" s="5" t="n">
+        <v>-0.091782</v>
       </c>
     </row>
     <row r="240">
@@ -28038,12 +27930,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 16)</t>
+          <t>Change in fair value of investments (note 8)</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -28108,12 +28000,10 @@
         </is>
       </c>
       <c r="Q240" s="5" t="n">
-        <v>0.29901</v>
-      </c>
-      <c r="R240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.178198</v>
+      </c>
+      <c r="R240" s="5" t="n">
+        <v>-2.118992</v>
       </c>
     </row>
     <row r="241">
@@ -28129,7 +28019,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Change in fair value of investments (note 7)</t>
+          <t>Impairment of promissory note receivable (note 7)</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -28188,11 +28078,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P241" s="5" t="n">
-        <v>-0.007141</v>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q241" s="5" t="n">
-        <v>0.178198</v>
+        <v>-0.12993</v>
       </c>
       <c r="R241" t="inlineStr">
         <is>
@@ -28213,14 +28105,10 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Interest expense (note 13)</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Impairment of intangible assets (note 10)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -28276,16 +28164,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P242" s="5" t="n">
-        <v>-0.013438</v>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q242" s="5" t="n">
-        <v>-0.008604000000000001</v>
-      </c>
-      <c r="R242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.057675</v>
+      </c>
+      <c r="R242" s="5" t="n">
+        <v>-0.42162</v>
       </c>
     </row>
     <row r="243">
@@ -28301,12 +28189,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Depreciation and amortization (notes 8, 9 and 10)</t>
+          <t>Net loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -28365,15 +28253,13 @@
         </is>
       </c>
       <c r="P243" s="5" t="n">
-        <v>-0.07538</v>
+        <v>-3.767772</v>
       </c>
       <c r="Q243" s="5" t="n">
-        <v>-0.09951400000000001</v>
-      </c>
-      <c r="R243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.451307</v>
+      </c>
+      <c r="R243" s="5" t="n">
+        <v>-4.342907</v>
       </c>
     </row>
     <row r="244">
@@ -28389,7 +28275,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Impairment of promissory note receivable (note 6)</t>
+          <t>Basic and diluted net loss per share (note 19) $</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -28448,16 +28334,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P244" s="5" t="n">
-        <v>-0.051843</v>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q244" s="5" t="n">
-        <v>-0.12993</v>
-      </c>
-      <c r="R244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="R244" s="5" t="n">
+        <v>-8e-08</v>
       </c>
     </row>
     <row r="245">
@@ -28468,15 +28354,19 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Loss on debt settlement (note 14)</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -28532,18 +28422,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P245" s="5" t="n">
+        <v>240.269604</v>
       </c>
       <c r="Q245" s="5" t="n">
-        <v>-0.1925</v>
-      </c>
-      <c r="R245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>39.780238</v>
+      </c>
+      <c r="R245" s="5" t="n">
+        <v>56.100295</v>
       </c>
     </row>
     <row r="246">
@@ -28554,15 +28440,19 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Impairment loss (note 9)</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
+          <t>Interest income $</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -28618,13 +28508,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P246" s="5" t="n">
+        <v>0.021843</v>
       </c>
       <c r="Q246" s="5" t="n">
-        <v>-1.057675</v>
+        <v>0.020055</v>
       </c>
       <c r="R246" t="inlineStr">
         <is>
@@ -28640,15 +28528,19 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per share (note 18) $</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -28705,10 +28597,10 @@
         </is>
       </c>
       <c r="P247" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.002056</v>
       </c>
       <c r="Q247" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.006015</v>
       </c>
       <c r="R247" t="inlineStr">
         <is>
@@ -28722,17 +28614,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>SALES $</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Stock-based compensation (note 16)</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -28748,11 +28640,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H248" s="5" t="n">
-        <v>0.001709</v>
-      </c>
-      <c r="I248" s="5" t="n">
-        <v>0.004793</v>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
@@ -28774,21 +28670,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N248" s="5" t="n">
-        <v>0.003883</v>
-      </c>
-      <c r="O248" s="5" t="n">
-        <v>0.139427</v>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q248" s="5" t="n">
+        <v>0.29901</v>
       </c>
       <c r="R248" t="inlineStr">
         <is>
@@ -28804,12 +28702,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Inventory - beginning of year</t>
+          <t>Change in fair value of investments (note 7)</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -28858,21 +28756,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N249" s="5" t="n">
-        <v>0.0172</v>
-      </c>
-      <c r="O249" s="5" t="n">
-        <v>0.0512</v>
-      </c>
-      <c r="P249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P249" s="5" t="n">
+        <v>-0.007141</v>
+      </c>
+      <c r="Q249" s="5" t="n">
+        <v>0.178198</v>
       </c>
       <c r="R249" t="inlineStr">
         <is>
@@ -28888,15 +28786,19 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Purchases</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>Interest expense (note 13)</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -28942,21 +28844,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N250" s="5" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="O250" s="5" t="n">
-        <v>0.197471</v>
-      </c>
-      <c r="P250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P250" s="5" t="n">
+        <v>-0.013438</v>
+      </c>
+      <c r="Q250" s="5" t="n">
+        <v>-0.008604000000000001</v>
       </c>
       <c r="R250" t="inlineStr">
         <is>
@@ -28972,15 +28874,19 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>COST OF SALES total</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>Depreciation and amortization (notes 8, 9 and 10)</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -29026,21 +28932,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N251" s="5" t="n">
-        <v>0.0512</v>
-      </c>
-      <c r="O251" s="5" t="n">
-        <v>0.248671</v>
-      </c>
-      <c r="P251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P251" s="5" t="n">
+        <v>-0.07538</v>
+      </c>
+      <c r="Q251" s="5" t="n">
+        <v>-0.09951400000000001</v>
       </c>
       <c r="R251" t="inlineStr">
         <is>
@@ -29056,12 +28962,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Inventory - end of year</t>
+          <t>Impairment of promissory note receivable (note 6)</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -29110,21 +29016,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N252" s="5" t="n">
-        <v>0.0512</v>
-      </c>
-      <c r="O252" s="5" t="n">
-        <v>0.172724</v>
-      </c>
-      <c r="P252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P252" s="5" t="n">
+        <v>-0.051843</v>
+      </c>
+      <c r="Q252" s="5" t="n">
+        <v>-0.12993</v>
       </c>
       <c r="R252" t="inlineStr">
         <is>
@@ -29140,19 +29046,15 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>GROSS PROFIT</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
+          <t>Loss on debt settlement (note 14)</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -29198,21 +29100,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N253" s="5" t="n">
-        <v>0.003883</v>
-      </c>
-      <c r="O253" s="5" t="n">
-        <v>0.06347999999999999</v>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q253" s="5" t="n">
+        <v>-0.1925</v>
       </c>
       <c r="R253" t="inlineStr">
         <is>
@@ -29228,19 +29132,15 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Impairment loss (note 9)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -29266,35 +29166,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J254" s="5" t="n">
-        <v>0.423696</v>
-      </c>
-      <c r="K254" s="5" t="n">
-        <v>0.543022</v>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M254" s="5" t="n">
-        <v>0.59783</v>
-      </c>
-      <c r="N254" s="5" t="n">
-        <v>2.59428</v>
-      </c>
-      <c r="O254" s="5" t="n">
-        <v>3.368625</v>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P254" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q254" s="5" t="n">
+        <v>-1.057675</v>
       </c>
       <c r="R254" t="inlineStr">
         <is>
@@ -29310,19 +29218,15 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Research and development</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>ResearchAndDevelopment</t>
-        </is>
-      </c>
+          <t>Basic and diluted net loss per share (note 18) $</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -29348,33 +29252,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J255" s="5" t="n">
-        <v>0.09780899999999999</v>
-      </c>
-      <c r="K255" s="5" t="n">
-        <v>0.092485</v>
-      </c>
-      <c r="L255" s="5" t="n">
-        <v>0.060666</v>
-      </c>
-      <c r="M255" s="5" t="n">
-        <v>0.01308</v>
-      </c>
-      <c r="N255" s="5" t="n">
-        <v>1.371386</v>
-      </c>
-      <c r="O255" s="5" t="n">
-        <v>0.805538</v>
-      </c>
-      <c r="P255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P255" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="Q255" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="R255" t="inlineStr">
         <is>
@@ -29388,17 +29300,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
+      <c r="B256" t="inlineStr"/>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Stock-based compensation (Note 12)</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr"/>
+          <t>SALES $</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -29414,15 +29326,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H256" s="5" t="n">
+        <v>0.001709</v>
+      </c>
+      <c r="I256" s="5" t="n">
+        <v>0.004793</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -29445,10 +29353,10 @@
         </is>
       </c>
       <c r="N256" s="5" t="n">
-        <v>4.574</v>
+        <v>0.003883</v>
       </c>
       <c r="O256" s="5" t="n">
-        <v>1.574</v>
+        <v>0.139427</v>
       </c>
       <c r="P256" t="inlineStr">
         <is>
@@ -29474,53 +29382,65 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E257" s="5" t="n">
-        <v>0.735429</v>
-      </c>
-      <c r="F257" s="5" t="n">
-        <v>0.868757</v>
+          <t>Inventory - beginning of year</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H257" s="5" t="n">
-        <v>0.355757</v>
-      </c>
-      <c r="I257" s="5" t="n">
-        <v>0.210342</v>
-      </c>
-      <c r="J257" s="5" t="n">
-        <v>0.996505</v>
-      </c>
-      <c r="K257" s="5" t="n">
-        <v>1.241437</v>
-      </c>
-      <c r="L257" s="5" t="n">
-        <v>0.406937</v>
-      </c>
-      <c r="M257" s="5" t="n">
-        <v>0.61091</v>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N257" s="5" t="n">
-        <v>8.539666</v>
+        <v>0.0172</v>
       </c>
       <c r="O257" s="5" t="n">
-        <v>5.748163</v>
+        <v>0.0512</v>
       </c>
       <c r="P257" t="inlineStr">
         <is>
@@ -29546,53 +29466,65 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>LOSS FROM OPERATIONS</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E258" s="5" t="n">
-        <v>-0.735429</v>
-      </c>
-      <c r="F258" s="5" t="n">
-        <v>-0.868757</v>
+          <t>Purchases</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H258" s="5" t="n">
-        <v>-0.354487</v>
-      </c>
-      <c r="I258" s="5" t="n">
-        <v>-0.205549</v>
-      </c>
-      <c r="J258" s="5" t="n">
-        <v>-0.965342</v>
-      </c>
-      <c r="K258" s="5" t="n">
-        <v>-1.227341</v>
-      </c>
-      <c r="L258" s="5" t="n">
-        <v>-0.400032</v>
-      </c>
-      <c r="M258" s="5" t="n">
-        <v>-0.607127</v>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N258" s="5" t="n">
-        <v>-8.535783</v>
+        <v>0.034</v>
       </c>
       <c r="O258" s="5" t="n">
-        <v>-5.684683</v>
+        <v>0.197471</v>
       </c>
       <c r="P258" t="inlineStr">
         <is>
@@ -29618,19 +29550,15 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>OTHER INCOME (EXPENSES)</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>COST OF SALES total</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -29666,17 +29594,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L259" s="5" t="n">
-        <v>-0.002789</v>
-      </c>
-      <c r="M259" s="5" t="n">
-        <v>-0.002978</v>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N259" s="5" t="n">
-        <v>-0.057978</v>
+        <v>0.0512</v>
       </c>
       <c r="O259" s="5" t="n">
-        <v>-0.151686</v>
+        <v>0.248671</v>
       </c>
       <c r="P259" t="inlineStr">
         <is>
@@ -29702,19 +29634,15 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>OTHER INCOME (EXPENSES)</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Loss on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Inventory - end of year</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -29745,11 +29673,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K260" s="5" t="n">
-        <v>-7.6e-05</v>
-      </c>
-      <c r="L260" s="5" t="n">
-        <v>-0.000203</v>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
@@ -29757,10 +29689,10 @@
         </is>
       </c>
       <c r="N260" s="5" t="n">
-        <v>-0.013561</v>
+        <v>0.0512</v>
       </c>
       <c r="O260" s="5" t="n">
-        <v>-0.04332</v>
+        <v>0.172724</v>
       </c>
       <c r="P260" t="inlineStr">
         <is>
@@ -29786,15 +29718,19 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>OTHER INCOME (EXPENSES)</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Loss on debt conversion (Note 12)</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>GROSS PROFIT</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -29841,12 +29777,10 @@
         </is>
       </c>
       <c r="N261" s="5" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="O261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003883</v>
+      </c>
+      <c r="O261" s="5" t="n">
+        <v>0.06347999999999999</v>
       </c>
       <c r="P261" t="inlineStr">
         <is>
@@ -29872,15 +29806,19 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>OTHER INCOME (EXPENSES)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Accretion expense (Note 11)</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -29906,33 +29844,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J262" s="5" t="n">
+        <v>0.423696</v>
+      </c>
+      <c r="K262" s="5" t="n">
+        <v>0.543022</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M262" s="5" t="n">
+        <v>0.59783</v>
+      </c>
+      <c r="N262" s="5" t="n">
+        <v>2.59428</v>
       </c>
       <c r="O262" s="5" t="n">
-        <v>-0.001383</v>
+        <v>3.368625</v>
       </c>
       <c r="P262" t="inlineStr">
         <is>
@@ -29958,17 +29888,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>OTHER INCOME (EXPENSES)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>OTHER INCOME (EXPENSES) total</t>
+          <t>Research and development</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>ResearchAndDevelopment</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -29996,25 +29926,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J263" s="5" t="n">
+        <v>0.09780899999999999</v>
       </c>
       <c r="K263" s="5" t="n">
-        <v>0.008813</v>
+        <v>0.092485</v>
       </c>
       <c r="L263" s="5" t="n">
-        <v>0.021899</v>
+        <v>0.060666</v>
       </c>
       <c r="M263" s="5" t="n">
-        <v>0.019555</v>
+        <v>0.01308</v>
       </c>
       <c r="N263" s="5" t="n">
-        <v>0.07453899999999999</v>
+        <v>1.371386</v>
       </c>
       <c r="O263" s="5" t="n">
-        <v>0.196389</v>
+        <v>0.805538</v>
       </c>
       <c r="P263" t="inlineStr">
         <is>
@@ -30040,19 +29968,15 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>OTHER INCOME (EXPENSES)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>NET LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Stock-based compensation (Note 12)</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -30083,20 +30007,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K264" s="5" t="n">
-        <v>-1.236154</v>
-      </c>
-      <c r="L264" s="5" t="n">
-        <v>-0.421931</v>
-      </c>
-      <c r="M264" s="5" t="n">
-        <v>-0.626682</v>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N264" s="5" t="n">
-        <v>-8.610322</v>
+        <v>4.574</v>
       </c>
       <c r="O264" s="5" t="n">
-        <v>-5.881072</v>
+        <v>1.574</v>
       </c>
       <c r="P264" t="inlineStr">
         <is>
@@ -30122,63 +30052,53 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>OTHER INCOME (EXPENSES)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>BASIC AND DILUTED LOSS PER SHARE</t>
+          <t>EXPENSES total</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="n">
+        <v>0.735429</v>
+      </c>
+      <c r="F265" s="5" t="n">
+        <v>0.868757</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H265" s="5" t="n">
+        <v>0.355757</v>
+      </c>
+      <c r="I265" s="5" t="n">
+        <v>0.210342</v>
+      </c>
+      <c r="J265" s="5" t="n">
+        <v>0.996505</v>
       </c>
       <c r="K265" s="5" t="n">
-        <v>-1e-08</v>
+        <v>1.241437</v>
       </c>
       <c r="L265" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.406937</v>
       </c>
       <c r="M265" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.61091</v>
       </c>
       <c r="N265" s="5" t="n">
-        <v>-4e-08</v>
+        <v>8.539666</v>
       </c>
       <c r="O265" s="5" t="n">
-        <v>-3e-08</v>
+        <v>5.748163</v>
       </c>
       <c r="P265" t="inlineStr">
         <is>
@@ -30204,63 +30124,53 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>OTHER INCOME (EXPENSES)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES</t>
+          <t>LOSS FROM OPERATIONS</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E266" s="5" t="n">
+        <v>-0.735429</v>
+      </c>
+      <c r="F266" s="5" t="n">
+        <v>-0.868757</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H266" s="5" t="n">
+        <v>-0.354487</v>
+      </c>
+      <c r="I266" s="5" t="n">
+        <v>-0.205549</v>
+      </c>
+      <c r="J266" s="5" t="n">
+        <v>-0.965342</v>
       </c>
       <c r="K266" s="5" t="n">
-        <v>148.520089</v>
+        <v>-1.227341</v>
       </c>
       <c r="L266" s="5" t="n">
-        <v>163.27069</v>
+        <v>-0.400032</v>
       </c>
       <c r="M266" s="5" t="n">
-        <v>163.796606</v>
+        <v>-0.607127</v>
       </c>
       <c r="N266" s="5" t="n">
-        <v>199.964619</v>
+        <v>-8.535783</v>
       </c>
       <c r="O266" s="5" t="n">
-        <v>228.453636</v>
+        <v>-5.684683</v>
       </c>
       <c r="P266" t="inlineStr">
         <is>
@@ -30284,15 +30194,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr"/>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>OTHER INCOME (EXPENSES)</t>
+        </is>
+      </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>REVENUE $</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -30315,28 +30229,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I267" s="5" t="n">
-        <v>0.004793</v>
-      </c>
-      <c r="J267" s="5" t="n">
-        <v>0.031163</v>
-      </c>
-      <c r="K267" s="5" t="n">
-        <v>0.014096</v>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L267" s="5" t="n">
-        <v>0.006905</v>
+        <v>-0.002789</v>
       </c>
       <c r="M267" s="5" t="n">
-        <v>0.003783</v>
+        <v>-0.002978</v>
       </c>
       <c r="N267" s="5" t="n">
-        <v>0.003883</v>
-      </c>
-      <c r="O267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.057978</v>
+      </c>
+      <c r="O267" s="5" t="n">
+        <v>-0.151686</v>
       </c>
       <c r="P267" t="inlineStr">
         <is>
@@ -30362,15 +30280,19 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER INCOME (EXPENSES)</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Stock-based compensation (Note 10)</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
+          <t>Loss on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -30401,15 +30323,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K268" s="5" t="n">
+        <v>-7.6e-05</v>
+      </c>
+      <c r="L268" s="5" t="n">
+        <v>-0.000203</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
@@ -30417,12 +30335,10 @@
         </is>
       </c>
       <c r="N268" s="5" t="n">
-        <v>4.574</v>
-      </c>
-      <c r="O268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.013561</v>
+      </c>
+      <c r="O268" s="5" t="n">
+        <v>-0.04332</v>
       </c>
       <c r="P268" t="inlineStr">
         <is>
@@ -30453,14 +30369,10 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>(Loss) gain on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
+          <t>Loss on debt conversion (Note 12)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -30501,11 +30413,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M269" s="5" t="n">
-        <v>0.00082</v>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N269" s="5" t="n">
-        <v>-0.013561</v>
+        <v>-0.003</v>
       </c>
       <c r="O269" t="inlineStr">
         <is>
@@ -30541,7 +30455,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Loss on debt conversion (Note 10)</t>
+          <t>Accretion expense (Note 11)</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -30590,13 +30504,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N270" s="5" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="O270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O270" s="5" t="n">
+        <v>-0.001383</v>
       </c>
       <c r="P270" t="inlineStr">
         <is>
@@ -30627,10 +30541,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Debenture accretion (Note 9)</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr"/>
+          <t>OTHER INCOME (EXPENSES) total</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -30661,28 +30579,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K271" s="5" t="n">
+        <v>0.008813</v>
+      </c>
+      <c r="L271" s="5" t="n">
+        <v>0.021899</v>
       </c>
       <c r="M271" s="5" t="n">
-        <v>-0.017397</v>
-      </c>
-      <c r="N271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.019555</v>
+      </c>
+      <c r="N271" s="5" t="n">
+        <v>0.07453899999999999</v>
+      </c>
+      <c r="O271" s="5" t="n">
+        <v>0.196389</v>
       </c>
       <c r="P271" t="inlineStr">
         <is>
@@ -30708,17 +30618,17 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER INCOME (EXPENSES)</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>General and administrative (Note 6)</t>
+          <t>NET LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -30752,25 +30662,19 @@
         </is>
       </c>
       <c r="K272" s="5" t="n">
-        <v>0.534285</v>
+        <v>-1.236154</v>
       </c>
       <c r="L272" s="5" t="n">
-        <v>0.249938</v>
-      </c>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.421931</v>
+      </c>
+      <c r="M272" s="5" t="n">
+        <v>-0.626682</v>
+      </c>
+      <c r="N272" s="5" t="n">
+        <v>-8.610322</v>
+      </c>
+      <c r="O272" s="5" t="n">
+        <v>-5.881072</v>
       </c>
       <c r="P272" t="inlineStr">
         <is>
@@ -30796,15 +30700,19 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER INCOME (EXPENSES)</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Stock-based compensation expense (Note 9)</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
+          <t>BASIC AND DILUTED LOSS PER SHARE</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -30836,25 +30744,19 @@
         </is>
       </c>
       <c r="K273" s="5" t="n">
-        <v>0.614667</v>
+        <v>-1e-08</v>
       </c>
       <c r="L273" s="5" t="n">
-        <v>0.096333</v>
-      </c>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="M273" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="N273" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="O273" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="P273" t="inlineStr">
         <is>
@@ -30885,10 +30787,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Accretion expense (Note 8)</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -30920,25 +30826,19 @@
         </is>
       </c>
       <c r="K274" s="5" t="n">
-        <v>-0.008737</v>
+        <v>148.520089</v>
       </c>
       <c r="L274" s="5" t="n">
-        <v>-0.018907</v>
-      </c>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>163.27069</v>
+      </c>
+      <c r="M274" s="5" t="n">
+        <v>163.796606</v>
+      </c>
+      <c r="N274" s="5" t="n">
+        <v>199.964619</v>
+      </c>
+      <c r="O274" s="5" t="n">
+        <v>228.453636</v>
       </c>
       <c r="P274" t="inlineStr">
         <is>
@@ -30962,17 +30862,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Shares    Share capital     reserve       reserve     debentures       Deficit         Total</t>
-        </is>
-      </c>
+      <c r="B275" t="inlineStr"/>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Comprehensive loss - - - - -</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>REVENUE $</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -30993,31 +30893,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I275" s="5" t="n">
+        <v>0.004793</v>
+      </c>
+      <c r="J275" s="5" t="n">
+        <v>0.031163</v>
       </c>
       <c r="K275" s="5" t="n">
-        <v>-1.236154</v>
+        <v>0.014096</v>
       </c>
       <c r="L275" s="5" t="n">
-        <v>-1.236154</v>
-      </c>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.006905</v>
+      </c>
+      <c r="M275" s="5" t="n">
+        <v>0.003783</v>
+      </c>
+      <c r="N275" s="5" t="n">
+        <v>0.003883</v>
       </c>
       <c r="O275" t="inlineStr">
         <is>
@@ -31048,12 +30940,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Shares    Share capital     reserve       reserve     debentures       Deficit         Total</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Changes 25,711,882 1,204,179 190,443 614,667 49,118</t>
+          <t>Stock-based compensation (Note 10)</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
@@ -31087,8 +30979,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K276" s="5" t="n">
-        <v>2.058407</v>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -31100,10 +30994,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N276" s="5" t="n">
+        <v>4.574</v>
       </c>
       <c r="O276" t="inlineStr">
         <is>
@@ -31134,15 +31026,19 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Shares    Share capital     reserve       reserve     debentures       Deficit         Total</t>
+          <t>OTHER INCOME (EXPENSES)</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2018 160,755,622 10,848,368 3,340,218 1,889,118 320,572</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>(Loss) gain on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -31173,21 +31069,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K277" s="5" t="n">
-        <v>-0.071592</v>
-      </c>
-      <c r="L277" s="5" t="n">
-        <v>-16.469868</v>
-      </c>
-      <c r="M277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M277" s="5" t="n">
+        <v>0.00082</v>
+      </c>
+      <c r="N277" s="5" t="n">
+        <v>-0.013561</v>
       </c>
       <c r="O277" t="inlineStr">
         <is>
@@ -31218,12 +31114,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Shares    Share capital     reserve       reserve     debentures       Deficit         Total</t>
+          <t>OTHER INCOME (EXPENSES)</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Changes 3,000,000 119,170 21,000 96,333 (29,380)</t>
+          <t>Loss on debt conversion (Note 10)</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -31257,8 +31153,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K278" s="5" t="n">
-        <v>0.207123</v>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -31270,10 +31168,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N278" s="5" t="n">
+        <v>-0.003</v>
       </c>
       <c r="O278" t="inlineStr">
         <is>
@@ -31304,12 +31200,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER INCOME (EXPENSES)</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Stock-based compensation expense</t>
+          <t>Debenture accretion (Note 9)</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -31338,21 +31234,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J279" s="5" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="K279" s="5" t="n">
-        <v>0.614667</v>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M279" s="5" t="n">
+        <v>-0.017397</v>
       </c>
       <c r="N279" t="inlineStr">
         <is>
@@ -31388,17 +31286,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>OTHER EXPENSE</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Loss on foreign exchange</t>
+          <t>General and administrative (Note 6)</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -31416,22 +31314,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H280" s="5" t="n">
-        <v>-0.001884</v>
-      </c>
-      <c r="I280" s="5" t="n">
-        <v>-0.000472</v>
-      </c>
-      <c r="J280" s="5" t="n">
-        <v>-0.000247</v>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K280" s="5" t="n">
-        <v>-7.6e-05</v>
-      </c>
-      <c r="L280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.534285</v>
+      </c>
+      <c r="L280" s="5" t="n">
+        <v>0.249938</v>
       </c>
       <c r="M280" t="inlineStr">
         <is>
@@ -31472,12 +31374,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>OTHER EXPENSE</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>LOSS $</t>
+          <t>Stock-based compensation expense (Note 9)</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -31506,16 +31408,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J281" s="5" t="n">
-        <v>-0.965589</v>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K281" s="5" t="n">
-        <v>-1.236154</v>
-      </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.614667</v>
+      </c>
+      <c r="L281" s="5" t="n">
+        <v>0.096333</v>
       </c>
       <c r="M281" t="inlineStr">
         <is>
@@ -31556,19 +31458,15 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>OTHER EXPENSE</t>
+          <t>OTHER INCOME (EXPENSES)</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>BASIC AND DILUTED LOSS PER SHARE</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Accretion expense (Note 8)</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -31594,16 +31492,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J282" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K282" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="L282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.008737</v>
+      </c>
+      <c r="L282" s="5" t="n">
+        <v>-0.018907</v>
       </c>
       <c r="M282" t="inlineStr">
         <is>
@@ -31644,12 +31542,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>OTHER EXPENSE</t>
+          <t>Shares    Share capital     reserve       reserve     debentures       Deficit         Total</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>AVERAGE WEIGHTED NUMBER OF COMMON SHARES</t>
+          <t>Comprehensive loss - - - - -</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -31678,16 +31576,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J283" s="5" t="n">
-        <v>116.625884</v>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K283" s="5" t="n">
-        <v>148.520089</v>
-      </c>
-      <c r="L283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.236154</v>
+      </c>
+      <c r="L283" s="5" t="n">
+        <v>-1.236154</v>
       </c>
       <c r="M283" t="inlineStr">
         <is>
@@ -31728,43 +31626,47 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares    Share capital     reserve       reserve     debentures       Deficit         Total</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>General and administrative (Note 5)</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E284" s="5" t="n">
-        <v>0.262407</v>
-      </c>
-      <c r="F284" s="5" t="n">
-        <v>0.317768</v>
+          <t>Changes 25,711,882 1,204,179 190,443 614,667 49,118</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H284" s="5" t="n">
-        <v>0.351857</v>
-      </c>
-      <c r="I284" s="5" t="n">
-        <v>0.210342</v>
-      </c>
-      <c r="J284" s="5" t="n">
-        <v>0.423696</v>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K284" s="5" t="n">
+        <v>2.058407</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -31810,12 +31712,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares    Share capital     reserve       reserve     debentures       Deficit         Total</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Stock-based compensation expense (Note 8)</t>
+          <t>Balance, July 31, 2018 160,755,622 10,848,368 3,340,218 1,889,118 320,572</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -31844,18 +31746,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J285" s="5" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K285" s="5" t="n">
+        <v>-0.071592</v>
+      </c>
+      <c r="L285" s="5" t="n">
+        <v>-16.469868</v>
       </c>
       <c r="M285" t="inlineStr">
         <is>
@@ -31896,19 +31796,15 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>OTHER EXPENSE</t>
+          <t>Shares    Share capital     reserve       reserve     debentures       Deficit         Total</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Changes 3,000,000 119,170 21,000 96,333 (29,380)</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -31924,19 +31820,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H286" s="5" t="n">
-        <v>-0.356371</v>
-      </c>
-      <c r="I286" s="5" t="n">
-        <v>-0.206021</v>
-      </c>
-      <c r="J286" s="5" t="n">
-        <v>-0.965589</v>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K286" s="5" t="n">
+        <v>0.207123</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -31982,12 +31882,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>OTHER EXPENSE</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per share (Note 10) $</t>
+          <t>Stock-based compensation expense</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -32006,19 +31906,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H287" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="I287" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J287" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.475</v>
+      </c>
+      <c r="K287" s="5" t="n">
+        <v>0.614667</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -32069,12 +31971,12 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares (Note 10)</t>
+          <t>Loss on foreign exchange</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -32093,18 +31995,16 @@
         </is>
       </c>
       <c r="H288" s="5" t="n">
-        <v>88.46055800000001</v>
+        <v>-0.001884</v>
       </c>
       <c r="I288" s="5" t="n">
-        <v>110.352437</v>
+        <v>-0.000472</v>
       </c>
       <c r="J288" s="5" t="n">
-        <v>116.625884</v>
-      </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.000247</v>
+      </c>
+      <c r="K288" s="5" t="n">
+        <v>-7.6e-05</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
@@ -32148,17 +32048,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr"/>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSE</t>
+        </is>
+      </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>LOSS $</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -32174,23 +32074,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H289" s="5" t="n">
-        <v>0.000439</v>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J289" s="5" t="n">
+        <v>-0.965589</v>
+      </c>
+      <c r="K289" s="5" t="n">
+        <v>-1.236154</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -32234,15 +32132,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr"/>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSE</t>
+        </is>
+      </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>GROSS PROFIT</t>
+          <t>BASIC AND DILUTED LOSS PER SHARE</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>GrossProfit</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -32260,21 +32162,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H290" s="5" t="n">
-        <v>0.00127</v>
-      </c>
-      <c r="I290" s="5" t="n">
-        <v>0.004793</v>
-      </c>
-      <c r="J290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J290" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="K290" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
@@ -32320,12 +32222,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER EXPENSE</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Interest (Note 7)</t>
+          <t>AVERAGE WEIGHTED NUMBER OF COMMON SHARES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -32344,23 +32246,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H291" s="5" t="n">
-        <v>0.0039</v>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J291" s="5" t="n">
+        <v>116.625884</v>
+      </c>
+      <c r="K291" s="5" t="n">
+        <v>148.520089</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -32411,35 +32311,31 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Interest (Notes 7 and 8)</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr"/>
+          <t>General and administrative (Note 5)</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E292" s="5" t="n">
-        <v>0.473022</v>
+        <v>0.262407</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>0.550989</v>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.317768</v>
+      </c>
+      <c r="G292" s="5" t="n">
+        <v>0.387135</v>
+      </c>
+      <c r="H292" s="5" t="n">
+        <v>0.351857</v>
+      </c>
+      <c r="I292" s="5" t="n">
+        <v>0.210342</v>
+      </c>
+      <c r="J292" s="5" t="n">
+        <v>0.423696</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
@@ -32490,24 +32386,24 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>OTHER INCOME (EXPENSE)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Loss on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E293" s="5" t="n">
-        <v>-0.041058</v>
-      </c>
-      <c r="F293" s="5" t="n">
-        <v>-0.021048</v>
+          <t>Stock-based compensation expense (Note 8)</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
@@ -32524,10 +32420,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J293" s="5" t="n">
+        <v>0.475</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
@@ -32578,42 +32472,42 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>OTHER INCOME (EXPENSE)</t>
+          <t>OTHER EXPENSE</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Reversal of statute barred management fees payable (Note 12)</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
+          <t>LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F294" s="5" t="n">
-        <v>1.749849</v>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H294" s="5" t="n">
+        <v>-0.356371</v>
+      </c>
+      <c r="I294" s="5" t="n">
+        <v>-0.206021</v>
+      </c>
+      <c r="J294" s="5" t="n">
+        <v>-0.965589</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
@@ -32664,40 +32558,38 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>OTHER INCOME (EXPENSE)</t>
+          <t>OTHER EXPENSE</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>OTHER INCOME (EXPENSE) total</t>
+          <t>Basic and diluted net loss per share (Note 10) $</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
-      <c r="E295" s="5" t="n">
-        <v>-0.041058</v>
-      </c>
-      <c r="F295" s="5" t="n">
-        <v>1.728801</v>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H295" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="I295" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="J295" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
@@ -32748,40 +32640,42 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>NET INCOME (LOSS) AND COMPREHENSIVE INCOME (LOSS) FOR</t>
+          <t>OTHER EXPENSE</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>THE YEAR $</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr"/>
-      <c r="E296" s="5" t="n">
-        <v>-0.776487</v>
-      </c>
-      <c r="F296" s="5" t="n">
-        <v>0.860044</v>
+          <t>Weighted average number of common shares (Note 10)</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H296" s="5" t="n">
+        <v>88.46055800000001</v>
+      </c>
+      <c r="I296" s="5" t="n">
+        <v>110.352437</v>
+      </c>
+      <c r="J296" s="5" t="n">
+        <v>116.625884</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
@@ -32830,36 +32724,34 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>NET INCOME (LOSS) AND COMPREHENSIVE INCOME (LOSS) FOR</t>
-        </is>
-      </c>
+      <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Basic and diluted net income (loss) per share (Note 11) $</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E297" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="F297" s="5" t="n">
-        <v>1e-08</v>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H297" s="5" t="n">
+        <v>0.000439</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
@@ -32918,83 +32810,1367 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
+      <c r="B298" t="inlineStr"/>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>GROSS PROFIT</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H298" s="5" t="n">
+        <v>0.00127</v>
+      </c>
+      <c r="I298" s="5" t="n">
+        <v>0.004793</v>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Interest (Note 7)</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H299" s="5" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Interest (Notes 7 and 8)</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" s="5" t="n">
+        <v>0.473022</v>
+      </c>
+      <c r="F300" s="5" t="n">
+        <v>0.550989</v>
+      </c>
+      <c r="G300" s="5" t="n">
+        <v>0.64397</v>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Stock options</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Stock options total</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F301" s="5" t="n">
+        <v>0.868757</v>
+      </c>
+      <c r="G301" s="5" t="n">
+        <v>1.084876</v>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Stock options</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>LOSS FROM OPERATIONS</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F302" s="5" t="n">
+        <v>-0.868757</v>
+      </c>
+      <c r="G302" s="5" t="n">
+        <v>-1.084876</v>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>OTHER INCOME (EXPENSE)</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Gain (loss) on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F303" s="5" t="n">
+        <v>-0.021048</v>
+      </c>
+      <c r="G303" s="5" t="n">
+        <v>0.00194</v>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>OTHER INCOME (EXPENSE)</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Reversal of statute barred payables (Note 12)</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F304" s="5" t="n">
+        <v>1.749849</v>
+      </c>
+      <c r="G304" s="5" t="n">
+        <v>1.151144</v>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>OTHER INCOME (EXPENSE)</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>OTHER INCOME (EXPENSE) total</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" s="5" t="n">
+        <v>-0.041058</v>
+      </c>
+      <c r="F305" s="5" t="n">
+        <v>1.728801</v>
+      </c>
+      <c r="G305" s="5" t="n">
+        <v>1.153084</v>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>OTHER INCOME (EXPENSE)</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>NET INCOME AND COMPREHENSIVE INCOME FOR THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F306" s="5" t="n">
+        <v>0.860044</v>
+      </c>
+      <c r="G306" s="5" t="n">
+        <v>0.068208</v>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>OTHER INCOME (EXPENSE)</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Basic and diluted net income per share (Note 11) $</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F307" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="G307" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>OTHER INCOME (EXPENSE)</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares (Note 11)</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F308" s="5" t="n">
+        <v>69.12002</v>
+      </c>
+      <c r="G308" s="5" t="n">
+        <v>78.093569</v>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>OTHER INCOME (EXPENSE)</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Loss on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="n">
+        <v>-0.041058</v>
+      </c>
+      <c r="F309" s="5" t="n">
+        <v>-0.021048</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>OTHER INCOME (EXPENSE)</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Reversal of statute barred management fees payable (Note 12)</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F310" s="5" t="n">
+        <v>1.749849</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
         <is>
           <t>NET INCOME (LOSS) AND COMPREHENSIVE INCOME (LOSS) FOR</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr">
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" s="5" t="n">
+        <v>-0.776487</v>
+      </c>
+      <c r="F311" s="5" t="n">
+        <v>0.860044</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>NET INCOME (LOSS) AND COMPREHENSIVE INCOME (LOSS) FOR</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Basic and diluted net income (loss) per share (Note 11) $</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E312" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F312" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>NET INCOME (LOSS) AND COMPREHENSIVE INCOME (LOSS) FOR</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
         <is>
           <t>Weighted average number of common shares (Note 11)</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr">
+      <c r="D313" t="inlineStr">
         <is>
           <t>BasicAverageShares</t>
         </is>
       </c>
-      <c r="E298" s="5" t="n">
+      <c r="E313" s="5" t="n">
         <v>66.77743100000001</v>
       </c>
-      <c r="F298" s="5" t="n">
+      <c r="F313" s="5" t="n">
         <v>69.19002</v>
       </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R298" t="inlineStr">
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
         <is>
           <t>-</t>
         </is>
